--- a/output/topology_excel/13714.xlsx
+++ b/output/topology_excel/13714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -487,7 +487,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -498,18 +498,18 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
         <v>18</v>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
         <v>18</v>
@@ -553,7 +553,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
         <v>18</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,18 +586,18 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,18 +608,18 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
@@ -641,21 +641,21 @@
         <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Wall</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,15 +674,15 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>367</v>
+        <v>179</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -696,18 +696,18 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>367</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>137</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>379</v>
+        <v>119</v>
       </c>
       <c r="F14" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>174</v>
+        <v>276</v>
       </c>
       <c r="F17" t="n">
         <v>18</v>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>275</v>
+        <v>151</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>276</v>
+        <v>143</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>159</v>
+        <v>258</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>202</v>
+        <v>137</v>
       </c>
       <c r="F22" t="n">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -927,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="F24" t="n">
         <v>19</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>258</v>
+        <v>174</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,32 +1004,208 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>159</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>159</v>
+      </c>
+      <c r="F28" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>7</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>80</v>
+      </c>
+      <c r="F29" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" t="n">
+        <v>13</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>177</v>
+      </c>
+      <c r="F30" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>162</v>
+      </c>
+      <c r="F31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" t="n">
         <v>9</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>143</v>
-      </c>
-      <c r="F27" t="n">
-        <v>18</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>174</v>
+      </c>
+      <c r="F32" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>392</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>175</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>79</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/13714.xlsx
+++ b/output/topology_excel/13714.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>144</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         <v>179</v>
       </c>
       <c r="F11" t="n">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -1117,7 +1117,7 @@
         <v>162</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
